--- a/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
+++ b/jpcore-r4/release/v1.2.0/CodeSystem-jp-observation-electrocardiogram-duration-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>
